--- a/excel/df_odp.xlsx
+++ b/excel/df_odp.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R275"/>
+  <dimension ref="A1:V275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,6 +518,26 @@
           <t>TempoPrevistoLavoraz</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>GestioneLotto</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>GestioneMatricola</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>CodFamiglia</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>CodMacrofamiglia</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -594,6 +614,22 @@
           <t>[{'TempoPrevistoLavoraz': 0.017}]</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>RIC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -672,6 +708,26 @@
       <c r="R3" t="inlineStr">
         <is>
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>IMP</t>
         </is>
       </c>
     </row>
@@ -754,6 +810,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -830,6 +906,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.75}]</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>IMB</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -910,6 +1006,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -990,6 +1106,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1070,6 +1206,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1150,6 +1306,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.44}, {'TempoPrevistoLavoraz': 0.4}]</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>IM-FMR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1230,6 +1406,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1306,6 +1502,26 @@
           <t>[{'TempoPrevistoLavoraz': 15.0}]</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1382,6 +1598,26 @@
           <t>[{'TempoPrevistoLavoraz': 15.0}]</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1458,6 +1694,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.733}]</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1538,6 +1794,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.03}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>IM-RSP</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1618,6 +1894,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1698,6 +1994,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1778,6 +2094,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1858,6 +2194,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1938,6 +2294,26 @@
           <t>[{'TempoPrevistoLavoraz': 4.25}, {'TempoPrevistoLavoraz': 0.417}]</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>IM-RSP</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -2018,6 +2394,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -2094,6 +2490,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.0}]</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -2170,6 +2586,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.0}]</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -2246,6 +2682,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.0}]</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2326,6 +2782,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2406,6 +2882,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2486,6 +2982,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2566,6 +3082,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2646,6 +3182,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.03}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>IM-RSP</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2722,6 +3278,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.05}]</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2798,6 +3374,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.15}]</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2874,6 +3470,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.02}]</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2950,6 +3566,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.0}]</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -3030,6 +3666,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -3110,6 +3766,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -3186,6 +3862,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.667}]</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -3262,6 +3958,26 @@
           <t>[{'TempoPrevistoLavoraz': 16.667}]</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -3338,6 +4054,26 @@
           <t>[{'TempoPrevistoLavoraz': 16.667}]</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -3418,6 +4154,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -3494,6 +4250,26 @@
           <t>[{'TempoPrevistoLavoraz': 4.8}]</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -3570,6 +4346,26 @@
           <t>[{'TempoPrevistoLavoraz': 4.8}]</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -3646,6 +4442,26 @@
           <t>[{'TempoPrevistoLavoraz': 4.8}]</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -3726,6 +4542,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -3806,6 +4642,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -3886,6 +4742,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3966,6 +4842,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -4042,6 +4938,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.83}]</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -4122,6 +5038,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -4202,6 +5138,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -4282,6 +5238,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -4362,6 +5338,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -4442,6 +5438,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -4522,6 +5538,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -4602,6 +5638,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -4682,6 +5738,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -4758,6 +5834,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.333}]</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -4834,6 +5930,26 @@
           <t>[{'TempoPrevistoLavoraz': 20.0}]</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -4910,6 +6026,26 @@
           <t>[{'TempoPrevistoLavoraz': 20.0}]</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -4986,6 +6122,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.633}]</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -5066,6 +6222,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -5146,6 +6322,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -5226,6 +6422,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -5306,6 +6522,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -5386,6 +6622,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -5462,6 +6718,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.25}]</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -5538,6 +6814,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.5}]</t>
         </is>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -5614,6 +6910,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -5694,6 +7010,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -5770,6 +7106,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.633}]</t>
         </is>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -5850,6 +7206,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -5930,6 +7306,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -6006,6 +7402,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.633}]</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -6086,6 +7502,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -6166,6 +7602,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -6242,6 +7698,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -6318,6 +7794,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.317}]</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -6398,6 +7894,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -6478,6 +7994,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -6554,6 +8090,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.0}]</t>
         </is>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -6630,6 +8186,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.0}]</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -6706,6 +8282,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.0}]</t>
         </is>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -6782,6 +8378,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.633}]</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -6862,6 +8478,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -6942,6 +8578,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -7022,6 +8678,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -7102,6 +8778,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -7182,6 +8878,26 @@
           <t>[{'TempoPrevistoLavoraz': 4.25}, {'TempoPrevistoLavoraz': 0.417}]</t>
         </is>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>IM-RSP</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -7258,6 +8974,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.167}]</t>
         </is>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -7334,6 +9070,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.167}]</t>
         </is>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -7410,6 +9166,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -7490,6 +9266,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -7570,6 +9366,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -7650,6 +9466,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -7730,6 +9566,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -7806,6 +9662,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.9}]</t>
         </is>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -7882,6 +9758,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.217}]</t>
         </is>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -7962,6 +9858,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -8042,6 +9958,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -8122,6 +10058,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -8202,6 +10158,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -8282,6 +10258,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -8362,6 +10358,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -8442,6 +10458,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -8522,6 +10558,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -8602,6 +10658,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -8682,6 +10758,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -8762,6 +10858,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -8842,6 +10958,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -8922,6 +11058,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -8998,6 +11154,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.5}]</t>
         </is>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -9074,6 +11250,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.667}]</t>
         </is>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -9150,6 +11346,26 @@
           <t>[{'TempoPrevistoLavoraz': 5.25}]</t>
         </is>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -9226,6 +11442,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.25}]</t>
         </is>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -9302,6 +11538,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.25}]</t>
         </is>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -9378,6 +11634,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -9454,6 +11730,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -9534,6 +11830,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -9614,6 +11930,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -9690,6 +12026,26 @@
           <t>[{'TempoPrevistoLavoraz': 5.0}]</t>
         </is>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -9766,6 +12122,26 @@
           <t>[{'TempoPrevistoLavoraz': 4.0}]</t>
         </is>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -9846,6 +12222,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.51}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>IM-RSP</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -9926,6 +12322,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -10006,6 +12422,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -10086,6 +12522,26 @@
           <t>[{'TempoPrevistoLavoraz': 4.25}, {'TempoPrevistoLavoraz': 0.417}]</t>
         </is>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>IM-RSP</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -10162,6 +12618,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.2}]</t>
         </is>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -10238,6 +12714,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.583}]</t>
         </is>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -10314,6 +12810,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.95}]</t>
         </is>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -10394,6 +12910,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -10474,6 +13010,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -10554,6 +13110,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -10634,6 +13210,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -10714,6 +13310,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -10794,6 +13410,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -10874,6 +13510,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -10954,6 +13610,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -11034,6 +13710,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -11110,6 +13806,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.333}]</t>
         </is>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -11190,6 +13906,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -11266,6 +14002,26 @@
           <t>[{'TempoPrevistoLavoraz': 8.0}]</t>
         </is>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -11342,6 +14098,26 @@
           <t>[{'TempoPrevistoLavoraz': 8.0}]</t>
         </is>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -11418,6 +14194,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.5}]</t>
         </is>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -11494,6 +14290,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -11574,6 +14390,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -11650,6 +14486,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.317}]</t>
         </is>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -11730,6 +14586,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -11810,6 +14686,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -11890,6 +14786,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -11970,6 +14886,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -12050,6 +14986,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -12126,6 +15082,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -12202,6 +15178,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -12278,6 +15274,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.167}]</t>
         </is>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -12354,6 +15370,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.167}]</t>
         </is>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -12430,6 +15466,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -12506,6 +15562,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.167}]</t>
         </is>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -12586,6 +15662,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -12666,6 +15762,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -12746,6 +15862,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -12826,6 +15962,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -12906,6 +16062,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -12986,6 +16162,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -13066,6 +16262,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -13146,6 +16362,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -13226,6 +16462,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -13306,6 +16562,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -13382,6 +16658,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -13462,6 +16758,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -13538,6 +16854,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.5}]</t>
         </is>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -13614,6 +16950,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.0}]</t>
         </is>
       </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -13690,6 +17046,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.9}]</t>
         </is>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -13770,6 +17146,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -13850,6 +17246,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -13930,6 +17346,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -14010,6 +17446,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -14090,6 +17546,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -14170,6 +17646,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -14250,6 +17746,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -14330,6 +17846,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -14410,6 +17946,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -14490,6 +18046,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -14566,6 +18142,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.0}]</t>
         </is>
       </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -14642,6 +18238,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.267}]</t>
         </is>
       </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -14718,6 +18334,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -14794,6 +18430,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.167}]</t>
         </is>
       </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -14870,6 +18526,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.167}]</t>
         </is>
       </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -14946,6 +18622,26 @@
           <t>[{'TempoPrevistoLavoraz': 6.167}]</t>
         </is>
       </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -15026,6 +18722,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -15106,6 +18822,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -15186,6 +18922,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -15266,6 +19022,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -15346,6 +19122,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -15426,6 +19222,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -15506,6 +19322,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -15586,6 +19422,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -15666,6 +19522,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -15746,6 +19622,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -15826,6 +19722,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -15902,6 +19818,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.733}]</t>
         </is>
       </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -15978,6 +19914,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.2}]</t>
         </is>
       </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -16054,6 +20010,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.5}]</t>
         </is>
       </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -16130,6 +20106,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.333}]</t>
         </is>
       </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -16206,6 +20202,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.5}]</t>
         </is>
       </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -16282,6 +20298,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.5}]</t>
         </is>
       </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -16358,6 +20394,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.667}]</t>
         </is>
       </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -16434,6 +20490,26 @@
           <t>[{'TempoPrevistoLavoraz': 5.0}]</t>
         </is>
       </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -16510,6 +20586,26 @@
           <t>[{'TempoPrevistoLavoraz': 15.867}]</t>
         </is>
       </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -16586,6 +20682,26 @@
           <t>[{'TempoPrevistoLavoraz': 15.867}]</t>
         </is>
       </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -16666,6 +20782,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
@@ -16742,6 +20878,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.317}]</t>
         </is>
       </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
@@ -16818,6 +20974,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.633}]</t>
         </is>
       </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
@@ -16898,6 +21074,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
@@ -16978,6 +21174,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -17058,6 +21274,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -17134,6 +21370,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.133}]</t>
         </is>
       </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -17210,6 +21466,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.5}]</t>
         </is>
       </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -17286,6 +21562,26 @@
           <t>[{'TempoPrevistoLavoraz': 4.8}]</t>
         </is>
       </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -17362,6 +21658,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.33}]</t>
         </is>
       </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -17438,6 +21754,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.3}]</t>
         </is>
       </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -17514,6 +21850,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.33}]</t>
         </is>
       </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -17590,6 +21946,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.3}]</t>
         </is>
       </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -17666,6 +22042,26 @@
           <t>[{'TempoPrevistoLavoraz': 15.0}]</t>
         </is>
       </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -17742,6 +22138,26 @@
           <t>[{'TempoPrevistoLavoraz': 15.0}]</t>
         </is>
       </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -17818,6 +22234,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.317}]</t>
         </is>
       </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -17898,6 +22334,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -17974,6 +22430,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.533}]</t>
         </is>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -18054,6 +22530,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -18134,6 +22630,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -18214,6 +22730,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -18294,6 +22830,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -18374,6 +22930,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -18454,6 +23030,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -18534,6 +23130,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -18614,6 +23230,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -18690,6 +23326,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.167}]</t>
         </is>
       </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -18770,6 +23426,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -18850,6 +23526,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.44}, {'TempoPrevistoLavoraz': 0.4}]</t>
         </is>
       </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>IM-FMR</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -18930,6 +23626,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.44}, {'TempoPrevistoLavoraz': 0.4}]</t>
         </is>
       </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>IM-FMR</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -19010,6 +23726,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -19090,6 +23826,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -19166,6 +23922,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.2}]</t>
         </is>
       </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -19242,6 +24018,26 @@
           <t>[{'TempoPrevistoLavoraz': 8.1}]</t>
         </is>
       </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -19318,6 +24114,26 @@
           <t>[{'TempoPrevistoLavoraz': 8.1}]</t>
         </is>
       </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -19394,6 +24210,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.8}]</t>
         </is>
       </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -19470,6 +24306,26 @@
           <t>[{'TempoPrevistoLavoraz': 4.8}]</t>
         </is>
       </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -19546,6 +24402,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -19622,6 +24498,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -19698,6 +24594,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -19774,6 +24690,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.333}]</t>
         </is>
       </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -19850,6 +24786,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.5}]</t>
         </is>
       </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -19926,6 +24882,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.667}]</t>
         </is>
       </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -20002,6 +24978,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.5}]</t>
         </is>
       </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -20082,6 +25078,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -20162,6 +25178,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -20242,6 +25278,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -20322,6 +25378,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -20402,6 +25478,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -20482,6 +25578,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -20562,6 +25678,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -20642,6 +25778,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -20722,6 +25878,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.53}, {'TempoPrevistoLavoraz': 0.517}]</t>
         </is>
       </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -20802,6 +25978,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -20882,6 +26078,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -20962,6 +26178,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -21042,6 +26278,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -21122,6 +26378,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.42}, {'TempoPrevistoLavoraz': 0.55}]</t>
         </is>
       </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -21202,6 +26478,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.05}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -21282,6 +26578,26 @@
           <t>[{'TempoPrevistoLavoraz': 3.53}, {'TempoPrevistoLavoraz': 0.45}]</t>
         </is>
       </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>IM-BTS</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -21358,6 +26674,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.317}]</t>
         </is>
       </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -21438,6 +26774,26 @@
           <t>[{'TempoPrevistoLavoraz': 2.46}, {'TempoPrevistoLavoraz': 0.583}]</t>
         </is>
       </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>IM-MIS</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -21514,6 +26870,26 @@
           <t>[{'TempoPrevistoLavoraz': 4.8}]</t>
         </is>
       </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -21590,6 +26966,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.83}]</t>
         </is>
       </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -21666,6 +27062,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.83}]</t>
         </is>
       </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -21742,6 +27158,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.83}]</t>
         </is>
       </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -21818,6 +27254,26 @@
           <t>[{'TempoPrevistoLavoraz': 0.83}]</t>
         </is>
       </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -21894,6 +27350,26 @@
           <t>[{'TempoPrevistoLavoraz': 1.667}]</t>
         </is>
       </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>IMP</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -21968,6 +27444,26 @@
       <c r="R275" t="inlineStr">
         <is>
           <t>[{'TempoPrevistoLavoraz': 1.1}]</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>IMP</t>
         </is>
       </c>
     </row>
